--- a/Data/Building/Context.Humidity.xlsx
+++ b/Data/Building/Context.Humidity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709257847</v>
+        <v>1711850468</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709277181</v>
+        <v>1711869083</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709255930</v>
+        <v>1711929439</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709270585</v>
+        <v>1711945604</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709337585</v>
+        <v>1712022184</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709354550</v>
+        <v>1712037981</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709357081</v>
+        <v>1712103521</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709422787</v>
+        <v>1712124582</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709442101</v>
+        <v>1712187147</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +766,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: Moist</t>
+          <t>Context.Humidity.state: Dry</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709513610</v>
+        <v>1712191442</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709530163</v>
+        <v>1712208230</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709596886</v>
+        <v>1712277647</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709616740</v>
+        <v>1712294628</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709684361</v>
+        <v>1712362992</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709709330</v>
+        <v>1712389199</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709777337</v>
+        <v>1712451062</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709796443</v>
+        <v>1712476507</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709853908</v>
+        <v>1712535237</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709871235</v>
+        <v>1712553357</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709941346</v>
+        <v>1712620850</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709959806</v>
+        <v>1712638534</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1710029880</v>
+        <v>1712714939</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1710047078</v>
+        <v>1712730061</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1710050014</v>
+        <v>1712796269</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1261,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1710116714</v>
+        <v>1712812544</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1710136617</v>
+        <v>1712880951</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1327,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Context.Humidity.state: ExcessivelyHumid</t>
+          <t>Context.Humidity.state: ComfortableHumidity</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1710201451</v>
+        <v>1712894694</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710222528</v>
+        <v>1712898429</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1397,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710288355</v>
+        <v>1712966720</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710313864</v>
+        <v>1712990261</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710383250</v>
+        <v>1713054727</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1496,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710404563</v>
+        <v>1713079398</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1529,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710461077</v>
+        <v>1713142303</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710478789</v>
+        <v>1713157852</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1595,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710545590</v>
+        <v>1713224113</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1628,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710564660</v>
+        <v>1713241531</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1661,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710634817</v>
+        <v>1713311467</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710653464</v>
+        <v>1713327469</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710719553</v>
+        <v>1713400261</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1760,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710737059</v>
+        <v>1713414212</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710806728</v>
+        <v>1713485194</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710826047</v>
+        <v>1713500876</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1859,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710894109</v>
+        <v>1713571887</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710919929</v>
+        <v>1713592692</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1925,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710981639</v>
+        <v>1713657897</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1711007320</v>
+        <v>1713681589</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1711070551</v>
+        <v>1713743624</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2024,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1711087383</v>
+        <v>1713760980</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1711151699</v>
+        <v>1713835084</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1711171569</v>
+        <v>1713850724</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1711237507</v>
+        <v>1713916536</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1711257907</v>
+        <v>1713935878</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1711324593</v>
+        <v>1714003557</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1711342875</v>
+        <v>1714018101</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1711411341</v>
+        <v>1714091562</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1711430032</v>
+        <v>1714105311</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1711500425</v>
+        <v>1714176480</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1711525331</v>
+        <v>1714198545</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2387,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1711587457</v>
+        <v>1714262652</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1711612966</v>
+        <v>1714285042</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
